--- a/artfynd/A 23969-2025 artfynd.xlsx
+++ b/artfynd/A 23969-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92006022</v>
+        <v>131740168</v>
       </c>
       <c r="B2" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
+          <t>Nystugan Sydväst, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566573.0907563095</v>
+        <v>566560</v>
       </c>
       <c r="R2" t="n">
-        <v>6520003.973807478</v>
+        <v>6520068</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-05-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,19 +760,231 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>92006022</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>566573</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6520004</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-05-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-05-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Caroline Ryding</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Kaj Almqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Holmen</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>102167935</v>
+      </c>
+      <c r="B4" t="n">
+        <v>108206</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223701</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig klofibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Crepis tectorum var. tectorum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nystugan 130 m SO, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566624</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6519808</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Göran Göransson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Göran Göransson, Göran Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23969-2025 artfynd.xlsx
+++ b/artfynd/A 23969-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740168</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92006022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,8 +1000,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102167935</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>